--- a/Progetto/previsioni_biodeg.xlsx
+++ b/Progetto/previsioni_biodeg.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Previsioni" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info_Modello" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Previsioni" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Info_Modello" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/Progetto/previsioni_biodeg.xlsx
+++ b/Progetto/previsioni_biodeg.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Previsioni" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Info_Modello" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Previsioni" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info_Modello" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,27 +430,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sample_ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Predicted_Class</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Class_Label</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Dominio</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Affidabilità</t>
         </is>
@@ -463,7 +475,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -486,7 +498,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -509,7 +521,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -532,7 +544,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -555,7 +567,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -578,7 +590,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -601,7 +613,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -624,7 +636,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -647,7 +659,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -670,7 +682,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -693,7 +705,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -716,7 +728,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -739,7 +751,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -762,7 +774,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -785,7 +797,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -808,7 +820,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -831,7 +843,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Altamente inaffidabile</t>
         </is>
       </c>
     </row>
@@ -854,7 +866,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -877,7 +889,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -900,7 +912,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -923,7 +935,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -946,7 +958,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -969,7 +981,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -992,7 +1004,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1027,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1050,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1073,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1096,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1119,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1142,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1165,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1188,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Altamente inaffidabile</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1211,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1234,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1257,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1268,7 +1280,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1291,7 +1303,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1326,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1349,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1372,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1395,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1418,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1441,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1464,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1487,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1510,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1521,7 +1533,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1556,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1579,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1602,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1625,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1648,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1671,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1694,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1717,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1740,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1751,7 +1763,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1786,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1809,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1832,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1855,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1878,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1889,7 +1901,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1924,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1935,7 +1947,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1970,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1993,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2016,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2039,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2062,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2085,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2096,7 +2108,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2131,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2154,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2165,7 +2177,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2200,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2223,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2234,7 +2246,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2257,7 +2269,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2292,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2315,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2338,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2361,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2384,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2407,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2418,7 +2430,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2453,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2476,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2499,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Altamente inaffidabile</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2522,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2533,7 +2545,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2568,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2591,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2614,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2637,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2660,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2683,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2706,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2729,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2752,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2775,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2798,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2809,7 +2821,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2832,7 +2844,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2855,7 +2867,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2890,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2913,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Altamente inaffidabile</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2936,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2959,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2982,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -2993,7 +3005,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3028,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3051,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3074,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3097,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3120,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3131,7 +3143,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3166,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3189,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -3200,7 +3212,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3235,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -3246,7 +3258,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3281,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3304,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3315,7 +3327,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3350,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3361,7 +3373,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3396,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3419,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3430,7 +3442,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3465,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Altamente inaffidabile</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3488,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3511,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -3522,7 +3534,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3557,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3580,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -3591,7 +3603,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3626,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3637,7 +3649,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3672,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3695,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3718,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -3729,7 +3741,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -3752,7 +3764,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3787,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3810,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3821,7 +3833,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3844,7 +3856,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3879,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3902,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3925,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3948,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3959,7 +3971,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -3982,7 +3994,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4005,7 +4017,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4040,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4063,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4074,7 +4086,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4109,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4132,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4155,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4166,7 +4178,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4201,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4224,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -4235,7 +4247,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4270,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4293,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4304,7 +4316,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4339,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4362,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4385,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4408,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4419,7 +4431,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4454,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4477,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Altamente inaffidabile</t>
         </is>
       </c>
     </row>
@@ -4488,7 +4500,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4523,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4546,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4569,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4580,7 +4592,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4615,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4638,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -4649,7 +4661,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4658,11 +4670,11 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -4672,7 +4684,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4707,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4718,7 +4730,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4753,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4764,7 +4776,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4787,7 +4799,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4822,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4833,7 +4845,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4868,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4891,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4914,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4937,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4948,7 +4960,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4983,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -4994,7 +5006,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5017,7 +5029,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5040,7 +5052,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5075,7 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5086,7 +5098,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5121,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5144,7 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5167,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5190,7 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5213,7 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5224,7 +5236,7 @@
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5247,7 +5259,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5282,7 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5293,7 +5305,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5316,7 +5328,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5351,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5362,7 +5374,7 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5385,7 +5397,7 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5420,7 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5431,7 +5443,7 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5466,7 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5477,7 +5489,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5500,7 +5512,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5535,7 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5546,7 +5558,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5569,7 +5581,7 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5604,7 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5615,7 +5627,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5638,7 +5650,7 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5661,7 +5673,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5684,7 +5696,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5719,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5730,7 +5742,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5753,7 +5765,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5788,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5799,7 +5811,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5834,7 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5845,7 +5857,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5880,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5891,7 +5903,7 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5926,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5949,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5960,7 +5972,7 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -5983,7 +5995,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6018,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6029,7 +6041,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6064,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6075,7 +6087,7 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6098,7 +6110,7 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6133,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6156,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6167,7 +6179,7 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6190,7 +6202,7 @@
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6225,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6236,7 +6248,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6271,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6294,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6317,7 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6328,7 +6340,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6351,7 +6363,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6374,7 +6386,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6397,7 +6409,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6420,7 +6432,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6443,7 +6455,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6478,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6489,7 +6501,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6512,7 +6524,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6547,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6558,7 +6570,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6567,11 +6579,11 @@
         <v>267</v>
       </c>
       <c r="B268" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -6581,7 +6593,7 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6590,11 +6602,11 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -6604,7 +6616,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6639,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6650,7 +6662,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6685,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6696,7 +6708,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6719,7 +6731,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6742,7 +6754,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6777,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6800,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6811,7 +6823,7 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6846,7 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6869,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6880,7 +6892,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6915,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6926,7 +6938,7 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6949,7 +6961,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6984,7 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -6995,7 +7007,7 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7030,7 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7053,7 @@
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7076,7 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7099,7 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7110,7 +7122,7 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7145,7 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7156,7 +7168,7 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7179,7 +7191,7 @@
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7202,7 +7214,7 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7237,7 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7248,7 +7260,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7271,7 +7283,7 @@
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7294,7 +7306,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7317,7 +7329,7 @@
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7340,7 +7352,7 @@
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7349,11 +7361,11 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7363,7 +7375,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7398,7 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7409,7 +7421,7 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7432,7 +7444,7 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7455,7 +7467,7 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7464,11 +7476,11 @@
         <v>306</v>
       </c>
       <c r="B307" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7478,7 +7490,7 @@
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7501,7 +7513,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7510,11 +7522,11 @@
         <v>308</v>
       </c>
       <c r="B309" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7524,7 +7536,7 @@
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7533,11 +7545,11 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7547,7 +7559,7 @@
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7570,7 +7582,7 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7605,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7616,7 +7628,7 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7639,7 +7651,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7662,7 +7674,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7685,7 +7697,7 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7694,11 +7706,11 @@
         <v>316</v>
       </c>
       <c r="B317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7708,7 +7720,7 @@
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7731,7 +7743,7 @@
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7766,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7763,11 +7775,11 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7777,7 +7789,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7800,7 +7812,7 @@
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7809,11 +7821,11 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -7823,7 +7835,7 @@
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7858,7 @@
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7881,7 @@
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7904,7 @@
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7915,7 +7927,7 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7950,7 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7961,7 +7973,7 @@
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7996,7 @@
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8007,7 +8019,7 @@
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8042,7 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8053,7 +8065,7 @@
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8088,7 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8099,7 +8111,7 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8134,7 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8145,7 +8157,7 @@
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8168,7 +8180,7 @@
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8191,7 +8203,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8214,7 +8226,7 @@
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8237,7 +8249,7 @@
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8260,7 +8272,7 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8283,7 +8295,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8306,7 +8318,7 @@
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8329,7 +8341,7 @@
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8352,7 +8364,7 @@
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8375,7 +8387,7 @@
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8398,7 +8410,7 @@
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8433,7 @@
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8456,7 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8467,7 +8479,7 @@
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8490,7 +8502,7 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8513,7 +8525,7 @@
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8536,7 +8548,7 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8559,7 +8571,7 @@
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8582,7 +8594,7 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8605,7 +8617,7 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8640,7 @@
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8651,7 +8663,7 @@
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8674,7 +8686,7 @@
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8697,7 +8709,7 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8732,7 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8743,7 +8755,7 @@
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8778,7 @@
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8789,7 +8801,7 @@
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8824,7 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8847,7 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8858,7 +8870,7 @@
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8881,7 +8893,7 @@
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8904,7 +8916,7 @@
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8939,7 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8962,7 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8973,7 +8985,7 @@
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -8996,7 +9008,7 @@
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9031,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9042,7 +9054,7 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9065,7 +9077,7 @@
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9100,7 @@
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9123,7 @@
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9134,7 +9146,7 @@
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9157,7 +9169,7 @@
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9166,11 +9178,11 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -9180,7 +9192,7 @@
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9215,7 @@
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9226,7 +9238,7 @@
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9249,7 +9261,7 @@
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Altamente inaffidabile</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9284,7 @@
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9295,7 +9307,7 @@
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9318,7 +9330,7 @@
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9353,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9364,7 +9376,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9399,7 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9422,7 @@
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9433,7 +9445,7 @@
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9468,7 @@
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9491,7 @@
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9502,7 +9514,7 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9525,7 +9537,7 @@
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9548,7 +9560,7 @@
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9571,7 +9583,7 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9594,7 +9606,7 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9617,7 +9629,7 @@
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9640,7 +9652,7 @@
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9675,7 @@
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9698,7 @@
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9709,7 +9721,7 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9732,7 +9744,7 @@
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9767,7 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9778,7 +9790,7 @@
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9787,11 +9799,11 @@
         <v>407</v>
       </c>
       <c r="B408" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -9801,7 +9813,7 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9836,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9847,7 +9859,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9870,7 +9882,7 @@
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9905,7 @@
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9916,7 +9928,7 @@
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9951,7 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9962,7 +9974,7 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -9985,7 +9997,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10008,7 +10020,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10031,7 +10043,7 @@
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10054,7 +10066,7 @@
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10077,7 +10089,7 @@
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10100,7 +10112,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10123,7 +10135,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10146,7 +10158,7 @@
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10181,7 @@
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10192,7 +10204,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10215,7 +10227,7 @@
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10250,7 @@
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10261,7 +10273,7 @@
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10284,7 +10296,7 @@
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10293,11 +10305,11 @@
         <v>429</v>
       </c>
       <c r="B430" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -10307,7 +10319,7 @@
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10330,7 +10342,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10365,7 @@
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10376,7 +10388,7 @@
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10399,7 +10411,7 @@
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10422,7 +10434,7 @@
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10445,7 +10457,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10468,7 +10480,7 @@
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10491,7 +10503,7 @@
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10514,7 +10526,7 @@
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10537,7 +10549,7 @@
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10560,7 +10572,7 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10595,7 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10618,7 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10629,7 +10641,7 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10652,7 +10664,7 @@
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10675,7 +10687,7 @@
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10698,7 +10710,7 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10721,7 +10733,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10744,7 +10756,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10767,7 +10779,7 @@
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10790,7 +10802,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10813,7 +10825,7 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -10836,7 +10848,7 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10859,7 +10871,7 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10882,7 +10894,7 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10905,7 +10917,7 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -10928,7 +10940,7 @@
       </c>
       <c r="E457" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10951,7 +10963,7 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10986,7 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -10997,7 +11009,7 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11020,7 +11032,7 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11029,11 +11041,11 @@
         <v>461</v>
       </c>
       <c r="B462" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -11043,7 +11055,7 @@
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11066,7 +11078,7 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11101,7 @@
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11112,7 +11124,7 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11135,7 +11147,7 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11158,7 +11170,7 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11181,7 +11193,7 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11216,7 @@
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11227,7 +11239,7 @@
       </c>
       <c r="E470" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11250,7 +11262,7 @@
       </c>
       <c r="E471" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11273,7 +11285,7 @@
       </c>
       <c r="E472" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11296,7 +11308,7 @@
       </c>
       <c r="E473" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11331,7 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11354,7 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11365,7 +11377,7 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11400,7 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11411,7 +11423,7 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11446,7 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11457,7 +11469,7 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11492,7 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11503,7 +11515,7 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11538,7 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11549,7 +11561,7 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11584,7 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11595,7 +11607,7 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11618,7 +11630,7 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11641,7 +11653,7 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11664,7 +11676,7 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11687,7 +11699,7 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11710,7 +11722,7 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11733,7 +11745,7 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11768,7 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11791,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11802,7 +11814,7 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11825,7 +11837,7 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11848,7 +11860,7 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11857,11 +11869,11 @@
         <v>497</v>
       </c>
       <c r="B498" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -11871,7 +11883,7 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11894,7 +11906,7 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11917,7 +11929,7 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11940,7 +11952,7 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11963,7 +11975,7 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -11986,7 +11998,7 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -12009,7 +12021,7 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12032,7 +12044,7 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12055,7 +12067,7 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12090,7 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12113,7 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12110,11 +12122,11 @@
         <v>508</v>
       </c>
       <c r="B509" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -12124,7 +12136,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12147,7 +12159,7 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12170,7 +12182,7 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12193,7 +12205,7 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12216,7 +12228,7 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12239,7 +12251,7 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12274,7 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12285,7 +12297,7 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12320,7 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12343,7 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12366,7 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12377,7 +12389,7 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12400,7 +12412,7 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12409,11 +12421,11 @@
         <v>521</v>
       </c>
       <c r="B522" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -12423,7 +12435,7 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12446,7 +12458,7 @@
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12469,7 +12481,7 @@
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12492,7 +12504,7 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12515,7 +12527,7 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12538,7 +12550,7 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12561,7 +12573,7 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12596,7 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12607,7 +12619,7 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12642,7 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12653,7 +12665,7 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12676,7 +12688,7 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12685,11 +12697,11 @@
         <v>533</v>
       </c>
       <c r="B534" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -12699,7 +12711,7 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12734,7 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12745,7 +12757,7 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12768,7 +12780,7 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12803,7 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12814,7 +12826,7 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12837,7 +12849,7 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12860,7 +12872,7 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12883,7 +12895,7 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12918,7 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12941,7 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12952,7 +12964,7 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12975,7 +12987,7 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -12998,7 +13010,7 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13021,7 +13033,7 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13044,7 +13056,7 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13079,7 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13090,7 +13102,7 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13113,7 +13125,7 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13136,7 +13148,7 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13159,7 +13171,7 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13182,7 +13194,7 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13205,7 +13217,7 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13228,7 +13240,7 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13251,7 +13263,7 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13274,7 +13286,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13297,7 +13309,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13332,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13343,7 +13355,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13366,7 +13378,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13389,7 +13401,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13412,7 +13424,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13421,11 +13433,11 @@
         <v>565</v>
       </c>
       <c r="B566" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -13435,7 +13447,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13458,7 +13470,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13481,7 +13493,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13504,7 +13516,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13527,7 +13539,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13550,7 +13562,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13573,7 +13585,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13596,7 +13608,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13619,7 +13631,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13642,7 +13654,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13665,7 +13677,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13688,7 +13700,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13711,7 +13723,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13734,7 +13746,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13757,7 +13769,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13780,7 +13792,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13803,7 +13815,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -13826,7 +13838,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13849,7 +13861,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13872,7 +13884,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13907,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13930,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13941,7 +13953,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13950,11 +13962,11 @@
         <v>588</v>
       </c>
       <c r="B589" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -13964,7 +13976,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -13973,11 +13985,11 @@
         <v>589</v>
       </c>
       <c r="B590" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -13987,7 +13999,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14010,7 +14022,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14033,7 +14045,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14056,7 +14068,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14079,7 +14091,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14114,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14125,7 +14137,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14148,7 +14160,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14171,7 +14183,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14194,7 +14206,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14217,7 +14229,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14240,7 +14252,7 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14263,7 +14275,7 @@
       </c>
       <c r="E602" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14298,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14309,7 +14321,7 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14332,7 +14344,7 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14355,7 +14367,7 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14390,7 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14401,7 +14413,7 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14424,7 +14436,7 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14447,7 +14459,7 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14470,7 +14482,7 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14493,7 +14505,7 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14516,7 +14528,7 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14539,7 +14551,7 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14562,7 +14574,7 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14585,7 +14597,7 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14608,7 +14620,7 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14631,7 +14643,7 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14654,7 +14666,7 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14677,7 +14689,7 @@
       </c>
       <c r="E620" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14700,7 +14712,7 @@
       </c>
       <c r="E621" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14723,7 +14735,7 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14746,7 +14758,7 @@
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14769,7 +14781,7 @@
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14792,7 +14804,7 @@
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14815,7 +14827,7 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14838,7 +14850,7 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14861,7 +14873,7 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14884,7 +14896,7 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14907,7 +14919,7 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14930,7 +14942,7 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14953,7 +14965,7 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14976,7 +14988,7 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -14999,7 +15011,7 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15022,7 +15034,7 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15045,7 +15057,7 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15068,7 +15080,7 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15091,7 +15103,7 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15114,7 +15126,7 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15137,7 +15149,7 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15160,7 +15172,7 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Poco inaffidabile</t>
         </is>
       </c>
     </row>
@@ -15169,11 +15181,11 @@
         <v>641</v>
       </c>
       <c r="B642" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -15183,7 +15195,7 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15206,7 +15218,7 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15229,7 +15241,7 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15252,7 +15264,7 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15275,7 +15287,7 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15298,7 +15310,7 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15321,7 +15333,7 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15344,7 +15356,7 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15353,11 +15365,11 @@
         <v>649</v>
       </c>
       <c r="B650" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Non Biodegradabile</t>
+          <t>Biodegradabile</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -15367,7 +15379,7 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15390,7 +15402,7 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15413,7 +15425,7 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15436,7 +15448,7 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15471,7 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15482,7 +15494,7 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15505,7 +15517,7 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15540,7 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15551,7 +15563,7 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15574,7 +15586,7 @@
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15597,7 +15609,7 @@
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15620,7 +15632,7 @@
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15643,7 +15655,7 @@
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15678,7 @@
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15689,7 +15701,7 @@
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15712,7 +15724,7 @@
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15735,7 +15747,7 @@
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15758,7 +15770,7 @@
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15781,7 +15793,7 @@
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Alta</t>
+          <t>Affidabile</t>
         </is>
       </c>
     </row>
@@ -15804,7 +15816,7 @@
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Altamente inaffidabile</t>
         </is>
       </c>
     </row>
@@ -15827,7 +15839,7 @@
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Altamente inaffidabile</t>
         </is>
       </c>
     </row>
@@ -15850,7 +15862,7 @@
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Bassa</t>
+          <t>Altamente inaffidabile</t>
         </is>
       </c>
     </row>
@@ -15869,12 +15881,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Parametro</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Valore</t>
         </is>
@@ -15980,7 +15992,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.8209</t>
+          <t>0.8575</t>
         </is>
       </c>
     </row>
@@ -15992,7 +16004,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.8200</t>
+          <t>0.8202</t>
         </is>
       </c>
     </row>
@@ -16004,7 +16016,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.7222</t>
+          <t>0.7500</t>
         </is>
       </c>
     </row>
@@ -16016,7 +16028,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.9178</t>
+          <t>0.8904</t>
         </is>
       </c>
     </row>

--- a/Progetto/previsioni_biodeg.xlsx
+++ b/Progetto/previsioni_biodeg.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Previsioni" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info_Modello" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Previsioni" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Info_Modello" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4670,11 +4670,11 @@
         <v>184</v>
       </c>
       <c r="B185" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -6579,11 +6579,11 @@
         <v>267</v>
       </c>
       <c r="B268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -6602,11 +6602,11 @@
         <v>268</v>
       </c>
       <c r="B269" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -7361,11 +7361,11 @@
         <v>301</v>
       </c>
       <c r="B302" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -7476,11 +7476,11 @@
         <v>306</v>
       </c>
       <c r="B307" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -7522,11 +7522,11 @@
         <v>308</v>
       </c>
       <c r="B309" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -7545,11 +7545,11 @@
         <v>309</v>
       </c>
       <c r="B310" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -7706,11 +7706,11 @@
         <v>316</v>
       </c>
       <c r="B317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -7775,11 +7775,11 @@
         <v>319</v>
       </c>
       <c r="B320" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -7821,11 +7821,11 @@
         <v>321</v>
       </c>
       <c r="B322" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -9178,11 +9178,11 @@
         <v>380</v>
       </c>
       <c r="B381" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -9799,11 +9799,11 @@
         <v>407</v>
       </c>
       <c r="B408" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -10305,11 +10305,11 @@
         <v>429</v>
       </c>
       <c r="B430" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -11041,11 +11041,11 @@
         <v>461</v>
       </c>
       <c r="B462" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -11869,11 +11869,11 @@
         <v>497</v>
       </c>
       <c r="B498" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -12122,11 +12122,11 @@
         <v>508</v>
       </c>
       <c r="B509" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
@@ -12421,11 +12421,11 @@
         <v>521</v>
       </c>
       <c r="B522" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -12697,11 +12697,11 @@
         <v>533</v>
       </c>
       <c r="B534" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -13433,11 +13433,11 @@
         <v>565</v>
       </c>
       <c r="B566" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -13962,11 +13962,11 @@
         <v>588</v>
       </c>
       <c r="B589" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -13985,11 +13985,11 @@
         <v>589</v>
       </c>
       <c r="B590" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -15181,11 +15181,11 @@
         <v>641</v>
       </c>
       <c r="B642" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -15365,11 +15365,11 @@
         <v>649</v>
       </c>
       <c r="B650" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Biodegradabile</t>
+          <t>Non Biodegradabile</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Argmax su Y dummy (assegnazione alla classe con ŷ maggiore)</t>
+          <t>True Discriminant (argmax: assegnazione alla classe con ŷ maggiore)</t>
         </is>
       </c>
     </row>
@@ -15992,7 +15992,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.8575</t>
+          <t>0.8209</t>
         </is>
       </c>
     </row>
@@ -16004,7 +16004,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.8202</t>
+          <t>0.8200</t>
         </is>
       </c>
     </row>
@@ -16016,7 +16016,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0.7500</t>
+          <t>0.7222</t>
         </is>
       </c>
     </row>
@@ -16028,7 +16028,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.8904</t>
+          <t>0.9178</t>
         </is>
       </c>
     </row>
